--- a/www/ig/fhir/ror/StructureDefinition-ror-practitionerrole.xlsx
+++ b/www/ig/fhir/ror/StructureDefinition-ror-practitionerrole.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3336" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3337" uniqueCount="549">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T09:54:01+00:00</t>
+    <t>2026-04-29T15:35:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
@@ -698,6 +698,9 @@
     <t>Extension créée dans le cadre du ROR pour définir l'identité d’exercice d’un professionnel</t>
   </si>
   <si>
+    <t>ExerciceProfessionnel (civiliteExercice,nomExercice,prenomExercice)</t>
+  </si>
+  <si>
     <t>PractitionerRole.extension:contracted</t>
   </si>
   <si>
@@ -1537,6 +1540,9 @@
     <t>Extension créée dans le cadre du ROR pour apporter un contexte à la plage horaire définie par la suite. Un planning peut être constitué de plusieurs plages horaires du même type ou de type différent.</t>
   </si>
   <si>
+    <t>typePlageHoraire</t>
+  </si>
+  <si>
     <t>PractitionerRole.availableTime.extension:ror-available-time-effective-opening-closing-date</t>
   </si>
   <si>
@@ -1553,6 +1559,9 @@
     <t>Extension créée dans le cadre du ROR pour décrire le planning d'activité d'un professionnel ou d'une offre.</t>
   </si>
   <si>
+    <t>debutDateEffective/finDateEffective</t>
+  </si>
+  <si>
     <t>PractitionerRole.availableTime.extension:ror-available-time-number-days-of-week</t>
   </si>
   <si>
@@ -1567,6 +1576,9 @@
   </si>
   <si>
     <t>Extension créée dans le cadre du ROR pour indiquer le numéro du jour dans la semaine.</t>
+  </si>
+  <si>
+    <t>jourSemaine</t>
   </si>
   <si>
     <t>PractitionerRole.availableTime.modifierExtension</t>
@@ -4449,9 +4461,11 @@
       <c r="AJ20" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="AK20" s="2"/>
+      <c r="AK20" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AL20" t="s" s="2">
-        <v>78</v>
+        <v>219</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>78</v>
@@ -4468,13 +4482,13 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>203</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>78</v>
@@ -4496,13 +4510,13 @@
         <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4588,10 +4602,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4706,10 +4720,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4824,10 +4838,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4853,13 +4867,13 @@
         <v>138</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4867,7 +4881,7 @@
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>78</v>
@@ -4909,7 +4923,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>91</v>
@@ -4944,10 +4958,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4970,13 +4984,13 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5006,10 +5020,10 @@
         <v>171</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>78</v>
@@ -5027,7 +5041,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5045,7 +5059,7 @@
         <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
@@ -5062,13 +5076,13 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>203</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>78</v>
@@ -5090,13 +5104,13 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5182,10 +5196,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5300,10 +5314,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5420,10 +5434,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5449,13 +5463,13 @@
         <v>138</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5463,7 +5477,7 @@
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>78</v>
@@ -5505,7 +5519,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>91</v>
@@ -5540,10 +5554,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5566,13 +5580,13 @@
         <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5623,7 +5637,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5641,7 +5655,7 @@
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -5658,13 +5672,13 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>203</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>78</v>
@@ -5686,13 +5700,13 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5778,10 +5792,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5896,10 +5910,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6016,10 +6030,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6045,13 +6059,13 @@
         <v>138</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6059,7 +6073,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>78</v>
@@ -6101,7 +6115,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>91</v>
@@ -6136,10 +6150,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6162,13 +6176,13 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6219,7 +6233,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6237,7 +6251,7 @@
         <v>78</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
@@ -6254,13 +6268,13 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>203</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>78</v>
@@ -6282,13 +6296,13 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6374,13 +6388,13 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>203</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>78</v>
@@ -6402,13 +6416,13 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6494,10 +6508,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6523,16 +6537,16 @@
         <v>116</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>119</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -6581,7 +6595,7 @@
         <v>122</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6616,10 +6630,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6642,17 +6656,17 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -6701,7 +6715,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6719,27 +6733,27 @@
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6762,70 +6776,70 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="P40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q40" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="R40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="P40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q40" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="R40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6846,24 +6860,24 @@
         <v>78</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6886,19 +6900,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>78</v>
@@ -6947,7 +6961,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6959,7 +6973,7 @@
         <v>104</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>78</v>
@@ -6968,24 +6982,24 @@
         <v>78</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7008,16 +7022,16 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7067,7 +7081,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7079,10 +7093,10 @@
         <v>104</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>78</v>
@@ -7091,7 +7105,7 @@
         <v>78</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>78</v>
@@ -7102,10 +7116,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7128,16 +7142,16 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7187,7 +7201,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7199,7 +7213,7 @@
         <v>104</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>78</v>
@@ -7211,7 +7225,7 @@
         <v>78</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>78</v>
@@ -7222,10 +7236,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7248,19 +7262,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -7289,7 +7303,7 @@
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -7307,7 +7321,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7322,19 +7336,19 @@
         <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>78</v>
@@ -7342,10 +7356,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7368,16 +7382,16 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7406,10 +7420,10 @@
         <v>184</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>78</v>
@@ -7425,7 +7439,7 @@
         <v>122</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7446,13 +7460,13 @@
         <v>78</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>78</v>
@@ -7460,13 +7474,13 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>78</v>
@@ -7488,16 +7502,16 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7527,7 +7541,7 @@
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>78</v>
@@ -7545,7 +7559,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7560,19 +7574,19 @@
         <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>78</v>
@@ -7580,13 +7594,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>78</v>
@@ -7608,16 +7622,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7647,7 +7661,7 @@
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>78</v>
@@ -7665,7 +7679,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7680,19 +7694,19 @@
         <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>78</v>
@@ -7700,13 +7714,13 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>78</v>
@@ -7728,16 +7742,16 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7767,7 +7781,7 @@
       </c>
       <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>78</v>
@@ -7785,7 +7799,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7800,19 +7814,19 @@
         <v>105</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>78</v>
@@ -7820,13 +7834,13 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>78</v>
@@ -7848,16 +7862,16 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7887,7 +7901,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>78</v>
@@ -7905,7 +7919,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7920,19 +7934,19 @@
         <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>78</v>
@@ -7940,13 +7954,13 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>78</v>
@@ -7968,16 +7982,16 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8007,7 +8021,7 @@
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>78</v>
@@ -8025,7 +8039,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8040,19 +8054,19 @@
         <v>105</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>78</v>
@@ -8060,13 +8074,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>78</v>
@@ -8088,16 +8102,16 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8127,7 +8141,7 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>78</v>
@@ -8145,7 +8159,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8160,19 +8174,19 @@
         <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>78</v>
@@ -8180,13 +8194,13 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>78</v>
@@ -8208,16 +8222,16 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8247,7 +8261,7 @@
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>78</v>
@@ -8265,7 +8279,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8280,19 +8294,19 @@
         <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>78</v>
@@ -8300,13 +8314,13 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>78</v>
@@ -8328,16 +8342,16 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8367,7 +8381,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>78</v>
@@ -8385,7 +8399,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8400,19 +8414,19 @@
         <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>78</v>
@@ -8420,13 +8434,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>78</v>
@@ -8448,16 +8462,16 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8487,7 +8501,7 @@
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8505,7 +8519,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8520,19 +8534,19 @@
         <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>78</v>
@@ -8540,13 +8554,13 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>78</v>
@@ -8568,16 +8582,16 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8607,7 +8621,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>78</v>
@@ -8625,7 +8639,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8640,19 +8654,19 @@
         <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>78</v>
@@ -8660,10 +8674,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8686,16 +8700,16 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8745,7 +8759,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8757,7 +8771,7 @@
         <v>104</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>78</v>
@@ -8769,21 +8783,21 @@
         <v>78</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8806,16 +8820,16 @@
         <v>78</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8865,7 +8879,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8877,19 +8891,19 @@
         <v>104</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>78</v>
@@ -8900,10 +8914,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8926,17 +8940,17 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -8985,7 +8999,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8997,22 +9011,22 @@
         <v>104</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>78</v>
@@ -9020,10 +9034,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9138,10 +9152,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9256,13 +9270,13 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="B61" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="B61" t="s" s="2">
-        <v>416</v>
-      </c>
       <c r="C61" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>78</v>
@@ -9284,13 +9298,13 @@
         <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9376,13 +9390,13 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>78</v>
@@ -9404,13 +9418,13 @@
         <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9496,13 +9510,13 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>78</v>
@@ -9524,13 +9538,13 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9616,10 +9630,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9645,13 +9659,13 @@
         <v>180</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9680,10 +9694,10 @@
         <v>171</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>78</v>
@@ -9701,7 +9715,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9710,7 +9724,7 @@
         <v>91</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>105</v>
@@ -9722,13 +9736,13 @@
         <v>78</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>78</v>
@@ -9736,10 +9750,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9765,16 +9779,16 @@
         <v>109</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
@@ -9823,7 +9837,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9841,16 +9855,16 @@
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>78</v>
@@ -9858,10 +9872,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9887,16 +9901,16 @@
         <v>180</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9924,10 +9938,10 @@
         <v>171</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>78</v>
@@ -9945,7 +9959,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9966,13 +9980,13 @@
         <v>78</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>78</v>
@@ -9980,10 +9994,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10006,16 +10020,16 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10065,7 +10079,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10100,10 +10114,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10126,16 +10140,16 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10185,7 +10199,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10197,7 +10211,7 @@
         <v>104</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>78</v>
@@ -10209,10 +10223,10 @@
         <v>107</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>78</v>
@@ -10220,10 +10234,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10246,16 +10260,16 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10305,7 +10319,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10323,13 +10337,13 @@
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
@@ -10340,10 +10354,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10458,10 +10472,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10578,13 +10592,13 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="B72" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="B72" t="s" s="2">
-        <v>484</v>
-      </c>
       <c r="C72" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>78</v>
@@ -10606,13 +10620,13 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10681,7 +10695,7 @@
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>78</v>
+        <v>491</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -10698,13 +10712,13 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>78</v>
@@ -10726,13 +10740,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10801,7 +10815,7 @@
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>78</v>
+        <v>497</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -10818,13 +10832,13 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>78</v>
@@ -10846,13 +10860,13 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10921,7 +10935,7 @@
         <v>78</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>78</v>
+        <v>503</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
@@ -10938,14 +10952,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10967,16 +10981,16 @@
         <v>116</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>119</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -11025,7 +11039,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11060,10 +11074,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11089,13 +11103,13 @@
         <v>180</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11124,28 +11138,28 @@
         <v>171</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="Z76" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11169,7 +11183,7 @@
         <v>78</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>78</v>
@@ -11180,10 +11194,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11206,13 +11220,13 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11263,7 +11277,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11287,7 +11301,7 @@
         <v>78</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>78</v>
@@ -11298,10 +11312,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11324,16 +11338,16 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11383,7 +11397,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11401,13 +11415,13 @@
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>78</v>
@@ -11418,10 +11432,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11444,16 +11458,16 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="M79" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11503,7 +11517,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11521,13 +11535,13 @@
         <v>78</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>78</v>
@@ -11538,10 +11552,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11564,13 +11578,13 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11621,7 +11635,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11645,7 +11659,7 @@
         <v>78</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>78</v>
@@ -11656,10 +11670,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11774,10 +11788,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11894,14 +11908,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -11923,16 +11937,16 @@
         <v>116</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>119</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
@@ -11981,7 +11995,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12016,10 +12030,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12045,13 +12059,13 @@
         <v>109</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12101,7 +12115,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>91</v>
@@ -12136,10 +12150,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12162,16 +12176,16 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12221,7 +12235,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12233,7 +12247,7 @@
         <v>104</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>78</v>
@@ -12242,10 +12256,10 @@
         <v>78</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>78</v>
@@ -12256,10 +12270,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12285,13 +12299,13 @@
         <v>109</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12341,7 +12355,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12365,7 +12379,7 @@
         <v>78</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>78</v>
@@ -12376,10 +12390,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12402,19 +12416,19 @@
         <v>78</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>78</v>
@@ -12463,7 +12477,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12475,7 +12489,7 @@
         <v>104</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>78</v>
@@ -12487,7 +12501,7 @@
         <v>78</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>78</v>
